--- a/nr-add-p-ins-intro-note/ig/ValueSet-fr-core-vs-encounter-class.xlsx
+++ b/nr-add-p-ins-intro-note/ig/ValueSet-fr-core-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:31:56+00:00</t>
+    <t>2024-07-08T11:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-p-ins-intro-note/ig/ValueSet-fr-core-vs-encounter-class.xlsx
+++ b/nr-add-p-ins-intro-note/ig/ValueSet-fr-core-vs-encounter-class.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:40:54+00:00</t>
+    <t>2024-07-08T11:41:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
